--- a/docs/bulk-templates/stores_sample.xlsx
+++ b/docs/bulk-templates/stores_sample.xlsx
@@ -446,330 +446,394 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>customer_code</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>uid</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>address</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pincode</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>lat</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>uid</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>contact_no</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>contact_email</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>contact_person</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>vendor_uid</t>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>outlet_status</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>YG000000026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>ST-101</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>VBL Store - Andheri</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Plot 4, Andheri East</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>400069</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="F2" s="2" t="n">
         <v>19.1197</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="G2" s="2" t="n">
         <v>72.8468</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>ST-101</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>02233440001</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>andheri@vbl.example</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Store Mgr A</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>VND-001</t>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>YG000000033</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>ST-102</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>VBL Store - Salt Lake</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Sector V, Salt Lake</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>700091</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="F3" s="2" t="n">
         <v>22.5697</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="G3" s="2" t="n">
         <v>88.4336</v>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>ST-102</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>03344550002</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>saltlake@vbl.example</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Store Mgr B</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>VND-001</t>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>YG000000037</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>ST-103</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>VBL Store - Koramangala</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>80 Ft Road, Koramangala</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>560095</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="F4" s="2" t="n">
         <v>12.9352</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="G4" s="2" t="n">
         <v>77.6245</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>ST-103</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>08044550003</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>koramangala@vbl.example</t>
+        </is>
+      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>VND-001</t>
+          <t>Store Mgr C</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>YG000000038</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>ST-104</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>VBL Store - Hitech City</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Cyber Towers, Madhapur</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>500081</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="F5" s="2" t="n">
         <v>17.4483</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="G5" s="2" t="n">
         <v>78.39149999999999</v>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>ST-104</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>04044550004</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>hitechcity@vbl.example</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Store Mgr C</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>VND-002</t>
+          <t>Store Mgr D</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>YG000101108</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>ST-105</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
           <t>VBL Store - Vaishali Nagar</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Vaishali Nagar Main Rd</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>302021</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="F6" s="2" t="n">
         <v>26.9124</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="G6" s="2" t="n">
         <v>75.73050000000001</v>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>ST-105</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>01414550005</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>vaishali@vbl.example</t>
+        </is>
+      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>VND-002</t>
+          <t>Store Mgr E</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>YG000101109</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>ST-106</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
           <t>VBL Store - Anna Nagar</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>2nd Ave, Anna Nagar</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>600040</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="F7" s="2" t="n">
         <v>13.085</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="G7" s="2" t="n">
         <v>80.2101</v>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>ST-106</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>04444550006</t>
+        </is>
+      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Store Mgr D</t>
+          <t>annanagar@vbl.example</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>VND-001</t>
+          <t>Store Mgr F</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
     </row>
@@ -784,7 +848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -812,7 +876,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>customer_code</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -822,14 +886,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Store name.</t>
+          <t>Customer Code — the key that decides update vs. create. Must be unique.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>uid</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -839,14 +903,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Full store address.</t>
+          <t>Store UID. Mandatory, and unique across all stores.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>pincode</t>
+          <t>name</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -856,14 +920,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PIN code.</t>
+          <t>Store name.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>lat</t>
+          <t>address</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -873,14 +937,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latitude (decimal).</t>
+          <t>Full store address.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>pincode</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -890,92 +954,109 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Longitude (decimal).</t>
+          <t>PIN code.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>uid</t>
+          <t>lat</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Store UID — used as the de-dupe key on re-upload.</t>
+          <t>Latitude (decimal), between -90 and 90.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>contact_no</t>
+          <t>long</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Store contact phone.</t>
+          <t>Longitude (decimal), between -180 and 180.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>contact_no</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Store contact email.</t>
+          <t>Store contact phone.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>contact_person</t>
+          <t>contact_email</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Store contact person.</t>
+          <t>Store contact email. Must be a valid address.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>vendor_uid</t>
+          <t>contact_person</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Store contact person.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>outlet_status</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Vendor this store belongs to (must exist), e.g. VND-001.</t>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Outlet status from the customer master, e.g. ACTIVE.</t>
         </is>
       </c>
     </row>

--- a/docs/bulk-templates/stores_sample.xlsx
+++ b/docs/bulk-templates/stores_sample.xlsx
@@ -446,20 +446,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="25" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -470,50 +469,45 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>uid</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>address</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>pincode</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>pincode</t>
+          <t>lat</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>lat</t>
+          <t>long</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>contact_no</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>contact_no</t>
+          <t>contact_email</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>contact_person</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>contact_person</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>outlet_status</t>
         </is>
@@ -527,46 +521,41 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ST-101</t>
+          <t>VBL Store - Andheri</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>VBL Store - Andheri</t>
+          <t>Plot 4, Andheri East</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Plot 4, Andheri East</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
           <t>400069</t>
         </is>
       </c>
+      <c r="E2" s="2" t="n">
+        <v>19.1197</v>
+      </c>
       <c r="F2" s="2" t="n">
-        <v>19.1197</v>
-      </c>
-      <c r="G2" s="2" t="n">
         <v>72.8468</v>
       </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>02233440001</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>02233440001</t>
+          <t>andheri@vbl.example</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>andheri@vbl.example</t>
+          <t>Store Mgr A</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>Store Mgr A</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -580,46 +569,41 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>ST-102</t>
+          <t>VBL Store - Salt Lake</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>VBL Store - Salt Lake</t>
+          <t>Sector V, Salt Lake</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Sector V, Salt Lake</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
           <t>700091</t>
         </is>
       </c>
+      <c r="E3" s="2" t="n">
+        <v>22.5697</v>
+      </c>
       <c r="F3" s="2" t="n">
-        <v>22.5697</v>
-      </c>
-      <c r="G3" s="2" t="n">
         <v>88.4336</v>
       </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>03344550002</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>03344550002</t>
+          <t>saltlake@vbl.example</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>saltlake@vbl.example</t>
+          <t>Store Mgr B</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>Store Mgr B</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -633,46 +617,41 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>ST-103</t>
+          <t>VBL Store - Koramangala</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>VBL Store - Koramangala</t>
+          <t>80 Ft Road, Koramangala</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>80 Ft Road, Koramangala</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
           <t>560095</t>
         </is>
       </c>
+      <c r="E4" s="2" t="n">
+        <v>12.9352</v>
+      </c>
       <c r="F4" s="2" t="n">
-        <v>12.9352</v>
-      </c>
-      <c r="G4" s="2" t="n">
         <v>77.6245</v>
       </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>08044550003</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>08044550003</t>
+          <t>koramangala@vbl.example</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>koramangala@vbl.example</t>
+          <t>Store Mgr C</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Store Mgr C</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -686,46 +665,41 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>ST-104</t>
+          <t>VBL Store - Hitech City</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>VBL Store - Hitech City</t>
+          <t>Cyber Towers, Madhapur</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Cyber Towers, Madhapur</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
           <t>500081</t>
         </is>
       </c>
+      <c r="E5" s="2" t="n">
+        <v>17.4483</v>
+      </c>
       <c r="F5" s="2" t="n">
-        <v>17.4483</v>
-      </c>
-      <c r="G5" s="2" t="n">
         <v>78.39149999999999</v>
       </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>04044550004</t>
+        </is>
+      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>04044550004</t>
+          <t>hitechcity@vbl.example</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>hitechcity@vbl.example</t>
+          <t>Store Mgr D</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>Store Mgr D</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -739,46 +713,41 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>ST-105</t>
+          <t>VBL Store - Vaishali Nagar</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>VBL Store - Vaishali Nagar</t>
+          <t>Vaishali Nagar Main Rd</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Vaishali Nagar Main Rd</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
           <t>302021</t>
         </is>
       </c>
+      <c r="E6" s="2" t="n">
+        <v>26.9124</v>
+      </c>
       <c r="F6" s="2" t="n">
-        <v>26.9124</v>
-      </c>
-      <c r="G6" s="2" t="n">
         <v>75.73050000000001</v>
       </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>01414550005</t>
+        </is>
+      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>01414550005</t>
+          <t>vaishali@vbl.example</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>vaishali@vbl.example</t>
+          <t>Store Mgr E</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>Store Mgr E</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -792,46 +761,41 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>ST-106</t>
+          <t>VBL Store - Anna Nagar</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>VBL Store - Anna Nagar</t>
+          <t>2nd Ave, Anna Nagar</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2nd Ave, Anna Nagar</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
           <t>600040</t>
         </is>
       </c>
+      <c r="E7" s="2" t="n">
+        <v>13.085</v>
+      </c>
       <c r="F7" s="2" t="n">
-        <v>13.085</v>
-      </c>
-      <c r="G7" s="2" t="n">
         <v>80.2101</v>
       </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>04444550006</t>
+        </is>
+      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>04444550006</t>
+          <t>annanagar@vbl.example</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>annanagar@vbl.example</t>
+          <t>Store Mgr F</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>Store Mgr F</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -848,7 +812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -886,14 +850,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Customer Code — the key that decides update vs. create. Must be unique.</t>
+          <t>Customer Code — the store's identifier and the key that decides update vs. create. An existing code updates that store in place and its tasks stay attached; a new code creates one. Must be unique.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>uid</t>
+          <t>name</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -903,14 +867,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Store UID. Mandatory, and unique across all stores.</t>
+          <t>Store name.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>address</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -920,14 +884,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Store name.</t>
+          <t>Full store address.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>pincode</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -937,14 +901,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Full store address.</t>
+          <t>PIN code.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>pincode</t>
+          <t>lat</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -954,14 +918,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PIN code.</t>
+          <t>Latitude (decimal), between -90 and 90.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>lat</t>
+          <t>long</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -971,14 +935,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latitude (decimal), between -90 and 90.</t>
+          <t>Longitude (decimal), between -180 and 180.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>contact_no</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -988,14 +952,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Longitude (decimal), between -180 and 180.</t>
+          <t>Store contact phone.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>contact_no</t>
+          <t>contact_email</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1005,14 +969,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Store contact phone.</t>
+          <t>Store contact email. Must be a valid address.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>contact_person</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1022,39 +986,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Store contact email. Must be a valid address.</t>
+          <t>Store contact person.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>contact_person</t>
+          <t>outlet_status</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
-        <is>
-          <t>Store contact person.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>outlet_status</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
         <is>
           <t>Outlet status from the customer master, e.g. ACTIVE.</t>
         </is>

--- a/docs/bulk-templates/stores_sample.xlsx
+++ b/docs/bulk-templates/stores_sample.xlsx
@@ -446,116 +446,185 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>customer_code</t>
+          <t>HOS</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>State_CD</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>Cust_CD</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>pincode</t>
+          <t>Cust_name</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>lat</t>
+          <t>CONT_PR</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>MOBILE_NO</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>contact_no</t>
+          <t>ADDR_1</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>ADDR_2</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>contact_person</t>
+          <t>ADDR_3</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>outlet_status</t>
+          <t>ADDR_4</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>ADDR_5</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ADDR_POSTAL</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>CHANNEL</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>SUB_CHANNEL</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>LATITUDE</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>LONGITUDE</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>CUST_STATUS</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>Rajesh Kumar</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>YG000000026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>VBL Store - Andheri</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Plot 4, Andheri East</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Store Mgr A</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>02233440001</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Plot 4</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Andheri East</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>400069</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>GT</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Grocery</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="n">
         <v>19.1197</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="P2" s="2" t="n">
         <v>72.8468</v>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>02233440001</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>andheri@vbl.example</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Store Mgr A</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -564,46 +633,73 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>Rajesh Kumar</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>YG000000033</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>VBL Store - Salt Lake</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Sector V, Salt Lake</t>
-        </is>
-      </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>700091</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>22.5697</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>88.4336</v>
+          <t>VBL Store - Powai</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Store Mgr B</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>02233440002</t>
+        </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>03344550002</t>
+          <t>Hiranandani Gardens</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>saltlake@vbl.example</t>
+          <t>Powai</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Store Mgr B</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>400076</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>GT</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Convenience</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>19.1176</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>72.90600000000001</v>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -612,46 +708,77 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>Anita Sharma</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>YG000000037</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>VBL Store - Koramangala</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>80 Ft Road, Koramangala</t>
-        </is>
-      </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>560095</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>12.9352</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>77.6245</v>
+          <t>VBL Store - Salt Lake</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Store Mgr C</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>03344550003</t>
+        </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>08044550003</t>
+          <t>Sector V</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>koramangala@vbl.example</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Store Mgr C</t>
+          <t>Salt Lake</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>700091</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Supermarket</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>22.5697</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>88.4336</v>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -660,46 +787,73 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>Vikram Patel</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>KA</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>YG000000038</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>VBL Store - Hitech City</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Cyber Towers, Madhapur</t>
-        </is>
-      </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>500081</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>17.4483</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>78.39149999999999</v>
+          <t>VBL Store - Koramangala</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Store Mgr D</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>08044550004</t>
+        </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>04044550004</t>
+          <t>80 Ft Road</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>hitechcity@vbl.example</t>
+          <t>Koramangala</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Store Mgr D</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>560095</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>GT</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Grocery</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>12.9352</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>77.6245</v>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -708,46 +862,77 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>Vikram Patel</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
           <t>YG000101108</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>VBL Store - Vaishali Nagar</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Vaishali Nagar Main Rd</t>
-        </is>
-      </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>302021</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>26.9124</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>75.73050000000001</v>
+          <t>VBL Store - Hitech City</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Store Mgr E</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>04044550005</t>
+        </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>01414550005</t>
+          <t>Cyber Towers</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>vaishali@vbl.example</t>
+          <t>Cyber Towers</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Store Mgr E</t>
+          <t>Madhapur</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>500081</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Supermarket</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>17.4483</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>78.39149999999999</v>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -756,48 +941,75 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>Anita Sharma</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
           <t>YG000101109</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>VBL Store - Anna Nagar</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>2nd Ave, Anna Nagar</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Store Mgr F</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>04444550006</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2nd Avenue</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Anna Nagar</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>600040</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>GT</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Convenience</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="n">
         <v>13.085</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="P7" s="2" t="n">
         <v>80.2101</v>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>04444550006</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>annanagar@vbl.example</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Store Mgr F</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>INACTIVE</t>
         </is>
       </c>
     </row>
@@ -812,10 +1024,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
   </cols>
@@ -840,41 +1052,41 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>customer_code</t>
+          <t>HOS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Customer Code — the store's identifier and the key that decides update vs. create. An existing code updates that store in place and its tasks stay attached; a new code creates one. Must be unique.</t>
+          <t>Head of sales / territory owner. Kept as source data; no field of its own.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>State_CD</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Store name.</t>
+          <t>State code. Kept as source data; no field of its own.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>Cust_CD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -884,14 +1096,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Full store address.</t>
+          <t>Customer Code — the store's identifier and the key that decides update vs. create. An existing code updates that store in place and its tasks stay attached; a new code creates one. Must be unique.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>pincode</t>
+          <t>Cust_name</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -901,48 +1113,48 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>PIN code.</t>
+          <t>Store name.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>lat</t>
+          <t>CONT_PR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latitude (decimal), between -90 and 90.</t>
+          <t>Contact person at the outlet.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>MOBILE_NO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Longitude (decimal), between -180 and 180.</t>
+          <t>Contact phone at the outlet.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>contact_no</t>
+          <t>ADDR_1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -952,48 +1164,48 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Store contact phone.</t>
+          <t>Address line 1. At least one ADDR_ line must have a real value.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>ADDR_2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Store contact email. Must be a valid address.</t>
+          <t>Address line 2.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>contact_person</t>
+          <t>ADDR_3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Store contact person.</t>
+          <t>Address line 3.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>outlet_status</t>
+          <t>ADDR_4</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1003,7 +1215,126 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Outlet status from the customer master, e.g. ACTIVE.</t>
+          <t>Address line 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>ADDR_5</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Address line 5. ADDR_1-ADDR_5 are joined into one address; blanks, '-' and 'NA' are dropped, and repeated lines are not duplicated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>ADDR_POSTAL</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PIN code.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>CHANNEL</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Sales channel. Kept as source data; no field of its own.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SUB_CHANNEL</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Sales sub-channel. Kept as source data; no field of its own.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>LATITUDE</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Latitude (decimal), between -90 and 90. A file spelling this LATTITUDE is also accepted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>LONGITUDE</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Longitude (decimal), between -180 and 180.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>CUST_STATUS</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Outlet status, e.g. ACTIVE. Stored as the store's outlet status.</t>
         </is>
       </c>
     </row>

--- a/docs/bulk-templates/stores_sample.xlsx
+++ b/docs/bulk-templates/stores_sample.xlsx
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">

--- a/docs/bulk-templates/stores_sample.xlsx
+++ b/docs/bulk-templates/stores_sample.xlsx
@@ -1334,7 +1334,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Outlet status, e.g. ACTIVE. Stored as the store's outlet status.</t>
+          <t>Outlet status, e.g. ACTIVE. A store already marked INACTIVE/Closed is frozen: its row is rejected rather than updated, unless this row sets the status back to ACTIVE.</t>
         </is>
       </c>
     </row>

--- a/docs/bulk-templates/stores_sample.xlsx
+++ b/docs/bulk-templates/stores_sample.xlsx
@@ -476,17 +476,17 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>State_CD</t>
+          <t>STATE_CD</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Cust_CD</t>
+          <t>CUST_CD</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Cust_name</t>
+          <t>CUST_NAME</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1069,7 +1069,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>State_CD</t>
+          <t>STATE_CD</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1086,7 +1086,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Cust_CD</t>
+          <t>CUST_CD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1103,7 +1103,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Cust_name</t>
+          <t>CUST_NAME</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">

--- a/docs/bulk-templates/stores_sample.xlsx
+++ b/docs/bulk-templates/stores_sample.xlsx
@@ -73,12 +73,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -1024,321 +1027,331 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="60" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Required</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Notes</t>
+          <t>Column names are matched on SPELLING ONLY. Upper or lower case makes no difference, and spaces, hyphens and underscores are treated the same - so CUST_CD, Cust_CD and "cust cd" are the same column. The headers on the Data sheet are all-caps; keep the wording, and the case is up to you. A sheet filled in with Caps Lock on uploads exactly like any other. Do not rename, reorder or delete columns - only the wording identifies them.</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
           <t>HOS</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Head of sales / territory owner. Kept as source data; no field of its own.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>STATE_CD</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>State code. Kept as source data; no field of its own.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>CUST_CD</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Customer Code — the store's identifier and the key that decides update vs. create. An existing code updates that store in place and its tasks stay attached; a new code creates one. Must be unique.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>CUST_NAME</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Store name.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>CONT_PR</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Contact person at the outlet.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>MOBILE_NO</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Contact phone at the outlet.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>ADDR_1</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Address line 1. At least one ADDR_ line must have a real value.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>ADDR_2</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Address line 2.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>ADDR_3</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Address line 3.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>ADDR_4</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Address line 4.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>ADDR_5</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Address line 5. ADDR_1-ADDR_5 are joined into one address; blanks, '-' and 'NA' are dropped, and repeated lines are not duplicated.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>ADDR_POSTAL</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>PIN code.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>CHANNEL</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Sales channel. Kept as source data; no field of its own.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>SUB_CHANNEL</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Sales sub-channel. Kept as source data; no field of its own.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>LATITUDE</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Latitude (decimal), between -90 and 90. A file spelling this LATTITUDE is also accepted.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>LONGITUDE</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Longitude (decimal), between -180 and 180.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>CUST_STATUS</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Outlet status, e.g. ACTIVE. A store already marked INACTIVE/Closed is frozen: its row is rejected rather than updated, unless this row sets the status back to ACTIVE.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>